--- a/03_Data_Analysis/Sprint_06/Unidad_02_Procesado_Datos_Externos_Web_Scraping_APIs/03_Practica_Obligatoria/data/mojo_data_backup.xlsx
+++ b/03_Data_Analysis/Sprint_06/Unidad_02_Procesado_Datos_Externos_Web_Scraping_APIs/03_Practica_Obligatoria/data/mojo_data_backup.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,59 +417,59 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Running Time</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Gross</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Theaters</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Total Gross</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Release Date</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Distributor</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Estimated</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>release</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>genre</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>running_time</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>theaters</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total_gross</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>release_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>distributor</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>estimated</t>
         </is>
       </c>
     </row>
@@ -493,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inside Out 2</t>
+          <t>Barbie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,27 +501,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$49,156,347</t>
+          <t>$33,554,745</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>424</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$49,156,347</t>
+          <t>$35,574,798</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Jun 21</t>
+          <t>Jul 21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -550,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deadpool &amp; Wolverine</t>
+          <t>The Super Mario Bros. Movie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,27 +558,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$23,895,185</t>
+          <t>$25,885,996</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$26,218,746</t>
+          <t>$29,917,392</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Apr 5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -607,7 +595,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gladiator II</t>
+          <t>Avatar: The Way of Water</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -627,27 +615,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$20,449,854</t>
+          <t>$25,885,456</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$22,021,377</t>
+          <t>$54,533,887</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nov 15</t>
+          <t>Dec 16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Paramount Pictures International</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -664,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Despicable Me 4</t>
+          <t>Oppenheimer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -684,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$20,193,576</t>
+          <t>$21,913,768</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,12 +682,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$22,554,267</t>
+          <t>$23,188,688</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jul 3</t>
+          <t>Jul 21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +709,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Moana 2</t>
+          <t>Elemental</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -741,22 +729,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>$16,900,691</t>
+          <t>$14,241,183</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$21,141,933</t>
+          <t>$14,241,750</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nov 29</t>
+          <t>Jul 14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +766,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dune: Part Two</t>
+          <t>Fast X</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,27 +786,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$14,904,688</t>
+          <t>$13,859,069</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$14,924,823</t>
+          <t>$13,859,069</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Mar 1</t>
+          <t>May 19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -835,7 +823,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Father There is Only One 4</t>
+          <t>Championext</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -855,27 +843,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>$12,978,587</t>
+          <t>$13,094,271</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$14,505,445</t>
+          <t>$12,877,645</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Jul 19</t>
+          <t>Aug 18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -892,7 +880,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Wild Robot</t>
+          <t>The Little Mermaid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -912,27 +900,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$10,688,456</t>
+          <t>$12,784,750</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$11,194,225</t>
+          <t>$12,784,750</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Oct 11</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -949,7 +937,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kung Fu Panda 4</t>
+          <t>Meg 2: The Trench</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -969,27 +957,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>$10,442,483</t>
+          <t>$12,673,104</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>369</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$10,667,137</t>
+          <t>$12,673,104</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mar 8</t>
+          <t>Aug 4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1006,7 +994,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>It Ends with Us</t>
+          <t>Indiana Jones and the Dial of Destiny</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1026,27 +1014,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>$9,467,465</t>
+          <t>$11,875,755</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>407</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$9,467,465</t>
+          <t>$13,009,168</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Aug 9</t>
+          <t>Jun 30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1063,7 +1051,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Beetlejuice Beetlejuice</t>
+          <t>Guardians of the Galaxy Vol. 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1083,27 +1071,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>$9,103,550</t>
+          <t>$11,826,005</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$9,199,542</t>
+          <t>$12,364,672</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sep 6</t>
+          <t>May 5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1120,7 +1108,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mufasa: The Lion King</t>
+          <t>Napoleon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1140,27 +1128,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$8,866,654</t>
+          <t>$10,317,561</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$21,927,688</t>
+          <t>$10,970,861</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dec 20</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1177,7 +1165,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Undercover</t>
+          <t>A Moroccan Affair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1197,27 +1185,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>$8,447,834</t>
+          <t>$9,804,743</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>624</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$10,416,680</t>
+          <t>$14,075,140</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Oct 11</t>
+          <t>Dec 1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Beta Fiction Spain</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1234,7 +1222,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Venom: The Last Dance</t>
+          <t>Spider-Man: Across the Spider-Verse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1254,22 +1242,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>$8,398,461</t>
+          <t>$9,036,917</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>$8,398,461</t>
+          <t>$9,036,917</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Jun 2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1291,7 +1279,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kingdom of the Planet of the Apes</t>
+          <t>Wonka</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1311,27 +1299,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>$7,809,979</t>
+          <t>$8,817,416</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>$7,809,979</t>
+          <t>$16,124,195</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>Dec 8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1348,7 +1336,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bad Boys: Ride or Die</t>
+          <t>Puss in Boots: The Last Wish</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1368,27 +1356,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>$7,009,853</t>
+          <t>$8,428,693</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$7,009,853</t>
+          <t>$11,776,830</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jun 7</t>
+          <t>Dec 21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1405,7 +1393,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anyone But You</t>
+          <t>The Hunger Games: The Ballad of Songbirds &amp; Snakes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1425,27 +1413,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>$6,819,135</t>
+          <t>$8,033,206</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>$6,819,135</t>
+          <t>$8,556,754</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Jan 19</t>
+          <t>Nov 17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Vértice 360</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1462,7 +1450,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wicked</t>
+          <t>Vacaciones de verano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1482,27 +1470,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>$6,428,525</t>
+          <t>$7,845,677</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>435</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>$7,562,082</t>
+          <t>$8,000,922</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Nov 22</t>
+          <t>Jul 7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1519,7 +1507,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alien: Romulus</t>
+          <t>The Nun II</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1539,27 +1527,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>$6,131,130</t>
+          <t>$7,145,722</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>$6,835,014</t>
+          <t>$7,158,175</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Sep 8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1576,7 +1564,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Odio el verano</t>
+          <t>Mummies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1596,27 +1584,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>$5,428,620</t>
+          <t>$6,443,543</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>399</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$5,428,620</t>
+          <t>$6,431,589</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aug 23</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1633,7 +1621,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Joker: Folie à Deux</t>
+          <t>Wish</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1653,27 +1641,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>$5,418,187</t>
+          <t>$6,163,633</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>$5,418,187</t>
+          <t>$7,344,994</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Oct 4</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Walt Disney Pictures</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1690,7 +1678,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Godzilla x Kong: The New Empire</t>
+          <t>Five Nights at Freddy's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1710,27 +1698,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>$5,377,442</t>
+          <t>$5,806,093</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>$6,845,899</t>
+          <t>$8,043,387</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mar 29</t>
+          <t>Nov 3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1747,7 +1735,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Ant-Man and the Wasp: Quantumania</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1767,27 +1755,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>$5,336,508</t>
+          <t>$5,762,900</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>$7,295,884</t>
+          <t>$5,762,900</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dec 22</t>
+          <t>Feb 17</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1804,7 +1792,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Garfield Movie</t>
+          <t>Killers of the Flower Moon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1824,27 +1812,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>$5,326,900</t>
+          <t>$5,662,082</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$6,601,763</t>
+          <t>$5,585,008</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>May 3</t>
+          <t>Oct 20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Paramount Pictures International</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1861,7 +1849,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ghostbusters: Frozen Empire</t>
+          <t>Creed III</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1881,27 +1869,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>$5,294,848</t>
+          <t>$5,566,039</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>$5,294,848</t>
+          <t>$5,566,039</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mar 22</t>
+          <t>Mar 3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1918,7 +1906,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Poor Things</t>
+          <t>The Equalizer 3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1938,27 +1926,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>$5,278,509</t>
+          <t>$5,281,976</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>359</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>$5,278,509</t>
+          <t>$5,281,976</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Jan 26</t>
+          <t>Sep 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1975,7 +1963,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wonka</t>
+          <t>Trolls Band Together</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1995,27 +1983,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>$5,256,139</t>
+          <t>$5,277,208</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>$16,124,195</t>
+          <t>$5,163,389</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Dec 8</t>
+          <t>Oct 27</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2032,7 +2020,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Buffalo Kids</t>
+          <t>One Hell of a Holiday!</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2052,27 +2040,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>$4,756,074</t>
+          <t>$5,176,254</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>$5,668,058</t>
+          <t>$5,176,254</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Apr 21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2089,7 +2077,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>La familia Benetón</t>
+          <t>A Haunting in Venice</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2109,27 +2097,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>$4,355,202</t>
+          <t>$5,043,029</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>$4,355,202</t>
+          <t>$5,043,029</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Mar 22</t>
+          <t>Sep 15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Beta Fiction Spain</t>
+          <t>Walt Disney Pictures</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2146,7 +2134,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A Moroccan Affair</t>
+          <t>John Wick: Chapter 4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2166,27 +2154,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>$4,270,397</t>
+          <t>$4,692,007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>$14,075,140</t>
+          <t>$4,704,335</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Dec 1</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2203,7 +2191,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trap</t>
+          <t>Insidious: The Red Door</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2223,27 +2211,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>$3,785,830</t>
+          <t>$4,514,691</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>$3,785,830</t>
+          <t>$4,764,794</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Aug 9</t>
+          <t>Jul 21</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2260,7 +2248,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Red One</t>
+          <t>Mari(dos)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2280,27 +2268,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>$3,770,628</t>
+          <t>$4,483,495</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>$4,167,734</t>
+          <t>$4,483,495</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Nov 8</t>
+          <t>Mar 10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2317,7 +2305,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Substance</t>
+          <t>Gran Turismo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2337,27 +2325,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>$3,624,826</t>
+          <t>$4,179,049</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>$3,631,454</t>
+          <t>$4,179,049</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Oct 11</t>
+          <t>Aug 11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>MUBI</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2374,7 +2362,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Juror #2</t>
+          <t>Evil Dead Rise</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2394,22 +2382,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>$3,579,238</t>
+          <t>$4,087,420</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>$3,652,286</t>
+          <t>$4,087,420</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Nov 1</t>
+          <t>Apr 21</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2431,7 +2419,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IF</t>
+          <t>The Exorcist: Believer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2451,27 +2439,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>$3,455,779</t>
+          <t>$4,037,587</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>$3,455,779</t>
+          <t>$4,040,305</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>May 17</t>
+          <t>Oct 6</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Paramount Pictures International</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2488,7 +2476,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>El 47</t>
+          <t>The Night My Dad Saved Christmas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2508,22 +2496,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>$3,360,870</t>
+          <t>$3,734,025</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>475</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>$4,302,516</t>
+          <t>$4,345,082</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Sep 6</t>
+          <t>Dec 1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2545,7 +2533,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Speak No Evil</t>
+          <t>The Flash</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2565,27 +2553,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>$3,353,782</t>
+          <t>$3,686,381</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>$3,406,298</t>
+          <t>$3,686,381</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Sep 13</t>
+          <t>Jun 16</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2602,7 +2590,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Fall Guy</t>
+          <t>Dungeons &amp; Dragons: Honor Among Thieves</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2622,27 +2610,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>$3,300,900</t>
+          <t>$3,607,808</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>359</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>$3,300,900</t>
+          <t>$3,685,302</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Mar 31</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Paramount Pictures International</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2659,7 +2647,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A House on Fire</t>
+          <t>The Beasts</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2679,27 +2667,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>$3,199,715</t>
+          <t>$3,558,223</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>$3,349,468</t>
+          <t>$7,376,891</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Jun 28</t>
+          <t>Nov 11</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>VerCine</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2716,7 +2704,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longlegs</t>
+          <t>M3GAN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2736,27 +2724,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>$3,087,180</t>
+          <t>$3,505,036</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>$3,102,078</t>
+          <t>$3,844,268</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Aug 2</t>
+          <t>Jan 4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2773,7 +2761,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Terrifier 3</t>
+          <t>PAW Patrol: The Mighty Movie</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2793,27 +2781,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>$3,065,987</t>
+          <t>$3,452,333</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>$3,645,244</t>
+          <t>$4,111,867</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Nov 1</t>
+          <t>Oct 11</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Selecta Visión</t>
+          <t>Paramount Pictures International</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2830,7 +2818,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aquaman and the Lost Kingdom</t>
+          <t>Transformers: Rise of the Beasts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2850,27 +2838,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>$3,053,002</t>
+          <t>$3,373,715</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>$6,639,154</t>
+          <t>$3,373,715</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Dec 22</t>
+          <t>Jun 9</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Paramount Pictures International</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2887,7 +2875,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A Quiet Place: Day One</t>
+          <t>The Creator</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2907,27 +2895,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>$2,950,230</t>
+          <t>$3,259,014</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>$3,084,407</t>
+          <t>$3,259,014</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Jun 27</t>
+          <t>Sep 29</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Paramount Pictures International</t>
+          <t>Walt Disney Pictures</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2944,7 +2932,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Furiosa: A Mad Max Saga</t>
+          <t>Aquaman and the Lost Kingdom</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2964,22 +2952,22 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>$2,802,385</t>
+          <t>$3,091,824</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>$2,802,385</t>
+          <t>$6,639,154</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>May 24</t>
+          <t>Dec 22</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3001,7 +2989,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Menudas piezas</t>
+          <t>The Marvels</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3021,27 +3009,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>$2,778,043</t>
+          <t>$3,018,439</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>$2,778,043</t>
+          <t>$3,297,579</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Apr 12</t>
+          <t>Nov 10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Paramount Pictures International</t>
+          <t>Walt Disney Pictures</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3058,7 +3046,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Room Next Door</t>
+          <t>The Pope's Exorcist</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3078,27 +3066,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>$2,534,799</t>
+          <t>$2,932,842</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>$2,534,180</t>
+          <t>$3,419,211</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Oct 18</t>
+          <t>Apr 7</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3115,7 +3103,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Beekeeper</t>
+          <t>Sound of Freedom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3135,27 +3123,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>$2,486,923</t>
+          <t>$2,790,378</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>$2,607,000</t>
+          <t>$3,042,013</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Jan 12</t>
+          <t>Oct 13</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sun Distribution</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3172,7 +3160,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Twisters</t>
+          <t>Saw X</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3192,27 +3180,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>$2,469,601</t>
+          <t>$2,782,773</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>$2,777,999</t>
+          <t>$2,782,773</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Jul 19</t>
+          <t>Sep 29</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>DeAPlaneta</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3229,7 +3217,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tarot</t>
+          <t>Teenage Mutant Ninja Turtles: Mutant Mayhem</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3249,27 +3237,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>$2,407,315</t>
+          <t>$2,733,466</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>$2,407,315</t>
+          <t>$2,735,509</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>Aug 25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Paramount Pictures International</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3286,7 +3274,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Civil War</t>
+          <t>Talk to Me</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3306,27 +3294,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>$2,256,209</t>
+          <t>$2,598,080</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>$2,257,584</t>
+          <t>$2,601,492</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Apr 19</t>
+          <t>Aug 11</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3343,7 +3331,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>One Life</t>
+          <t>Babylon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3363,27 +3351,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>$2,192,998</t>
+          <t>$2,483,459</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>$2,198,939</t>
+          <t>$2,483,459</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mar 22</t>
+          <t>Jan 20</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sun Distribution</t>
+          <t>Paramount Pictures International</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3400,7 +3388,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ask Me What You Want</t>
+          <t>El hotel de los líos. García y García 2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3420,27 +3408,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>$2,113,567</t>
+          <t>$2,432,785</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>$2,174,430</t>
+          <t>$2,432,785</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Nov 29</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3457,7 +3445,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dragonkeeper</t>
+          <t>Como Dios manda</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3477,27 +3465,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>$2,044,854</t>
+          <t>$2,318,817</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>$2,020,069</t>
+          <t>$2,318,817</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Apr 19</t>
+          <t>Jun 2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3514,7 +3502,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Count of Monte-Cristo</t>
+          <t>Scream VI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3534,27 +3522,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>$2,018,515</t>
+          <t>$2,219,043</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>$2,018,515</t>
+          <t>$2,219,043</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Aug 9</t>
+          <t>Mar 10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Beta Fiction Spain</t>
+          <t>Paramount Pictures International</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3571,7 +3559,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sonic the Hedgehog 3</t>
+          <t>Ruby Gillman: Teenage Kraken</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3591,27 +3579,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>$1,963,959</t>
+          <t>$2,168,127</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>346</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>$9,395,966</t>
+          <t>$2,168,633</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Dec 27</t>
+          <t>Jun 30</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Paramount Pictures International</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3628,7 +3616,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Madame Web</t>
+          <t>The Whale</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3648,27 +3636,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>$1,858,501</t>
+          <t>$2,087,509</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>$2,174,781</t>
+          <t>$2,097,850</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Feb 16</t>
+          <t>Jan 27</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Youplanet Pictures</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3685,7 +3673,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ferrari</t>
+          <t>A Man Called Otto</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3705,27 +3693,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>$1,807,331</t>
+          <t>$1,995,925</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>358</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>$1,809,698</t>
+          <t>$2,594,147</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Feb 9</t>
+          <t>Dec 30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Sun Distribution</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3742,7 +3730,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Valley of Shadows</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3762,27 +3750,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>$1,805,813</t>
+          <t>$1,947,056</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>$1,805,813</t>
+          <t>$7,295,884</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Jan 12</t>
+          <t>Dec 22</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3799,7 +3787,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Holdovers</t>
+          <t>The Kids Are Alright 2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3819,27 +3807,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>$1,785,905</t>
+          <t>$1,944,207</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>$1,890,308</t>
+          <t>$7,144,479</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Jan 3</t>
+          <t>Dec 2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3856,7 +3844,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Courier</t>
+          <t>The Fabelmans</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3876,22 +3864,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>$1,751,343</t>
+          <t>$1,922,197</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>302</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>$1,751,343</t>
+          <t>$1,922,779</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Jan 19</t>
+          <t>Feb 10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3913,7 +3901,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kraven the Hunter</t>
+          <t>Taylor Swift: The Eras Tour</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3933,27 +3921,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>$1,688,175</t>
+          <t>$1,908,537</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>$1,829,626</t>
+          <t>$1,908,537</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Dec 13</t>
+          <t>Oct 13</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Versión Digital</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3970,7 +3958,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Night Swim</t>
+          <t>Blue Beetle</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3990,27 +3978,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>$1,649,962</t>
+          <t>$1,858,757</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>$1,649,962</t>
+          <t>$1,858,757</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Feb 9</t>
+          <t>Aug 18</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4027,7 +4015,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cuerpo escombro</t>
+          <t>Operation Fortune: Ruse de Guerre</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4047,27 +4035,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>$1,644,714</t>
+          <t>$1,606,903</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>$1,644,714</t>
+          <t>$1,796,652</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Aug 9</t>
+          <t>Jan 4</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Diamond Films</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4084,7 +4072,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bob Marley: One Love</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4104,27 +4092,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>$1,637,946</t>
+          <t>$1,576,191</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>$1,880,242</t>
+          <t>$1,798,861</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Feb 14</t>
+          <t>Apr 7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Paramount Pictures International</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4141,7 +4129,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The First Omen</t>
+          <t>The Communion Girl</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4161,27 +4149,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>$1,633,017</t>
+          <t>$1,561,503</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>$1,633,017</t>
+          <t>$1,561,503</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Apr 5</t>
+          <t>Feb 10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4198,7 +4186,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Perfect Days</t>
+          <t>Haunted Mansion</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4218,27 +4206,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>$1,566,008</t>
+          <t>$1,561,204</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>$1,569,639</t>
+          <t>$1,561,204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Jan 12</t>
+          <t>Jul 28</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4255,7 +4243,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Challengers</t>
+          <t>The Boy and the Heron</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4275,27 +4263,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>$1,521,636</t>
+          <t>$1,559,646</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>$1,521,636</t>
+          <t>$1,881,640</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Oct 27</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Vértigo Films</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4312,7 +4300,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Anatomy of a Fall</t>
+          <t>Coup de Chance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4332,27 +4320,27 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>$1,480,821</t>
+          <t>$1,558,008</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>$2,729,780</t>
+          <t>$1,571,091</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Dec 8</t>
+          <t>Sep 29</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Elastica</t>
+          <t>Wanda Visión S.A.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4369,7 +4357,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>I Am Nevenka</t>
+          <t>The Teacher Who Promised the Sea</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4389,27 +4377,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>$1,470,137</t>
+          <t>$1,477,336</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>$1,499,275</t>
+          <t>$2,008,800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Sep 27</t>
+          <t>Nov 10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Filmax</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4426,7 +4414,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Conclave</t>
+          <t>Caged Wings</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4446,27 +4434,27 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>$1,464,350</t>
+          <t>$1,475,753</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>$6,124,692</t>
+          <t>$1,475,753</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Dec 20</t>
+          <t>Aug 25</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4483,7 +4471,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Zone of Interest</t>
+          <t>Alimañas</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4503,27 +4491,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>$1,428,246</t>
+          <t>$1,466,523</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>$1,434,487</t>
+          <t>$1,507,693</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Jan 19</t>
+          <t>Oct 27</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Elastica</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4540,7 +4528,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Red Virgin</t>
+          <t>Knock at the Cabin</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4560,27 +4548,27 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>$1,337,379</t>
+          <t>$1,414,341</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>$1,349,973</t>
+          <t>$1,414,341</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Sep 27</t>
+          <t>Feb 3</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Elastica</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4597,7 +4585,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blink Twice</t>
+          <t>Shazam! Fury of the Gods</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4617,22 +4605,22 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>$1,316,832</t>
+          <t>$1,402,279</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>$1,316,832</t>
+          <t>$1,402,279</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Aug 23</t>
+          <t>Mar 17</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4654,7 +4642,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>No Hard Feelings</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4674,27 +4662,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>$1,293,252</t>
+          <t>$1,342,820</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>$1,392,052</t>
+          <t>$1,342,820</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Nov 8</t>
+          <t>Jun 23</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4711,7 +4699,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Argylle</t>
+          <t>The Expendables 4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4731,27 +4719,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>$1,253,726</t>
+          <t>$1,298,370</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>$1,429,062</t>
+          <t>$1,298,370</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Feb 2</t>
+          <t>Sep 29</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Vértice 360</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4768,7 +4756,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fly Me to the Moon</t>
+          <t>After Everything</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4788,27 +4776,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>$1,214,241</t>
+          <t>$1,289,204</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>$1,214,241</t>
+          <t>$1,289,204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Jul 12</t>
+          <t>Sep 15</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4825,7 +4813,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wish</t>
+          <t>Titanic25 Year Anniversary</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4845,27 +4833,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>$1,181,361</t>
+          <t>$1,229,878</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>$7,344,994</t>
+          <t>$1,229,878</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Feb 10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4882,7 +4870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>¿Quién es quién?</t>
+          <t>The Boogeyman</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4902,27 +4890,27 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>$1,173,760</t>
+          <t>$1,190,241</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>$1,469,939</t>
+          <t>$1,190,241</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Dec 6</t>
+          <t>Jun 2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4939,7 +4927,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Políticamente incorrectos</t>
+          <t>Past Lives</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4959,27 +4947,27 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>$1,148,328</t>
+          <t>$1,187,488</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>132</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>$1,149,832</t>
+          <t>$1,353,127</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Feb 23</t>
+          <t>Nov 3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Elastica</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4996,7 +4984,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Back to Black</t>
+          <t>Triangle of Sadness</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5016,27 +5004,27 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>$1,115,550</t>
+          <t>$1,142,408</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>177</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>$1,116,398</t>
+          <t>$1,159,105</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>May 31</t>
+          <t>Feb 17</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Avalon</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5053,7 +5041,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>There's Still Tomorrow</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5073,27 +5061,27 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>$1,098,322</t>
+          <t>$1,123,267</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>$1,110,998</t>
+          <t>$1,123,267</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5110,7 +5098,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nosferatu</t>
+          <t>Anatomy of a Fall</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5130,27 +5118,27 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>$1,087,676</t>
+          <t>$1,113,137</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>$5,578,093</t>
+          <t>$2,729,780</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Dec 27</t>
+          <t>Dec 8</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Elastica</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5167,7 +5155,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Al otro barrio</t>
+          <t>The Banshees of Inisherin</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5187,27 +5175,27 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>$1,064,329</t>
+          <t>$1,082,846</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>$1,170,875</t>
+          <t>$1,082,846</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Dec 6</t>
+          <t>Feb 3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5224,7 +5212,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Watchers</t>
+          <t>All the Names of God</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5244,27 +5232,27 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>$1,009,565</t>
+          <t>$1,049,517</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>$1,009,565</t>
+          <t>$1,049,517</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Jun 7</t>
+          <t>Sep 15</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>TriPictures</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5281,7 +5269,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Abigail</t>
+          <t>Fatum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5301,22 +5289,22 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>$907,051</t>
+          <t>$1,021,093</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>$907,051</t>
+          <t>$1,021,093</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Apr 19</t>
+          <t>Apr 28</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5338,7 +5326,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Transformers One</t>
+          <t>Irati</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5358,27 +5346,27 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>$895,473</t>
+          <t>$1,000,973</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>$947,971</t>
+          <t>$1,036,865</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Sep 20</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Paramount Pictures International</t>
+          <t>Filmax</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5395,7 +5383,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Emilia Pérez</t>
+          <t>Me he hecho viral</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5415,27 +5403,27 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>$862,687</t>
+          <t>$1,000,827</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>$1,884,776</t>
+          <t>$1,216,305</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Dec 6</t>
+          <t>Oct 13</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Wanda Visión S.A.</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5452,7 +5440,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Demon Slayer: Kimetsu No Yaiba - To the Hashira Training</t>
+          <t>20,000 Species of Bees</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5472,27 +5460,27 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>$800,049</t>
+          <t>$995,482</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>$944,346</t>
+          <t>$1,108,932</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Feb 23</t>
+          <t>Apr 21</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>BTeam Pictures</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5509,7 +5497,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Teachers' Lounge</t>
+          <t>Plane</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5529,27 +5517,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>$769,714</t>
+          <t>$975,043</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>$779,852</t>
+          <t>$975,043</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Feb 2</t>
+          <t>Feb 10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>DeAPlaneta</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5566,7 +5554,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>10 Lives</t>
+          <t>Everything Everywhere All at Once</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5586,27 +5574,27 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>$769,334</t>
+          <t>$929,406</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>$769,334</t>
+          <t>$1,577,967</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Aug 2</t>
+          <t>Jun 3</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>Youplanet Pictures</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5623,7 +5611,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bagman</t>
+          <t>The Amazing Maurice</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5643,27 +5631,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>$762,371</t>
+          <t>$927,889</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>$763,166</t>
+          <t>$928,157</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Sep 27</t>
+          <t>Jan 20</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Flins &amp; Piniculas</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5680,7 +5668,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Haikyu!! The Dumpster Battle</t>
+          <t>Tár</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5700,27 +5688,27 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>$752,748</t>
+          <t>$922,371</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>197</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>$752,748</t>
+          <t>$922,371</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>May 31</t>
+          <t>Jan 27</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5737,7 +5725,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mean Girls</t>
+          <t>Asteroid City</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5757,27 +5745,27 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>$751,096</t>
+          <t>$899,964</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>171</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>$751,096</t>
+          <t>$899,964</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Jan 12</t>
+          <t>Jun 16</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Paramount Pictures International</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5794,7 +5782,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Immaculate</t>
+          <t>Jokes &amp; Cigarettes</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5814,27 +5802,27 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>$706,906</t>
+          <t>$873,249</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>$1,003,663</t>
+          <t>$982,894</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>May 1</t>
+          <t>Nov 3</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Diamond Films</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5851,7 +5839,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kinds of Kindness</t>
+          <t>Un Amor</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5871,27 +5859,27 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>$700,929</t>
+          <t>$869,026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>$704,704</t>
+          <t>$927,112</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Jun 28</t>
+          <t>Nov 10</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>BTeam Pictures</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5908,7 +5896,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Anora</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5928,27 +5916,27 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>$691,252</t>
+          <t>$856,152</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>$1,505,289</t>
+          <t>$856,152</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Oct 31</t>
+          <t>Nov 17</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5965,7 +5953,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Dead Don't Hurt</t>
+          <t>Cocaine Bear</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5985,27 +5973,27 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>$689,803</t>
+          <t>$851,679</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>$731,973</t>
+          <t>$851,679</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>Mar 31</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Wanda Visión S.A.</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6022,7 +6010,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cats in the Museum</t>
+          <t>Hypnotic</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6042,27 +6030,27 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>$675,838</t>
+          <t>$820,299</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>$677,144</t>
+          <t>$820,299</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Feb 23</t>
+          <t>Oct 27</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>VerCine</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6079,7 +6067,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Un lío de millones</t>
+          <t>Last Call, Rio!</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6099,22 +6087,22 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>$675,247</t>
+          <t>$790,387</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>$1,050,693</t>
+          <t>$790,387</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Dec 20</t>
+          <t>Aug 4</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6136,7 +6124,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Borderlands</t>
+          <t>The Three Musketeers - Part I: D'Artagnan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6156,27 +6144,27 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>$666,473</t>
+          <t>$789,412</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>$666,473</t>
+          <t>$790,284</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Aug 9</t>
+          <t>Apr 14</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Sun Distribution</t>
+          <t>DeAPlaneta</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6193,7 +6181,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Napoleon</t>
+          <t>Prey for the Devil</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6213,27 +6201,27 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>$653,300</t>
+          <t>$762,135</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>$10,970,861</t>
+          <t>$1,082,875</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Dec 30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Beta Fiction Spain</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6250,7 +6238,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Strangers: Chapter 1</t>
+          <t>Asterix &amp; Obelix: The Middle Kingdom</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6270,27 +6258,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>$639,812</t>
+          <t>$727,245</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>$639,812</t>
+          <t>$727,442</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Jul 12</t>
+          <t>Feb 3</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Diamond Films</t>
+          <t>Notorious Pictures</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6307,7 +6295,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Escape</t>
+          <t>Suzume</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6327,27 +6315,27 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>$634,893</t>
+          <t>$690,117</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>$694,075</t>
+          <t>$690,117</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Nov 1</t>
+          <t>Apr 14</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Beta Fiction Spain</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6364,7 +6352,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>La Navidad en sus manos</t>
+          <t>Just One Small Favor</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6384,27 +6372,27 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>$610,333</t>
+          <t>$679,797</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>$4,345,082</t>
+          <t>$676,236</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Dec 1</t>
+          <t>Nov 10</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6421,7 +6409,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Fallen Leaves</t>
+          <t>Mi otro Jon</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6441,27 +6429,27 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>$596,597</t>
+          <t>$666,921</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>$781,961</t>
+          <t>$669,778</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Dec 29</t>
+          <t>Oct 20</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Avalon</t>
+          <t>Wanda Visión S.A.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6478,7 +6466,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Arthur the King</t>
+          <t>Cobweb</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6498,27 +6486,27 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>$594,507</t>
+          <t>$646,418</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>$594,507</t>
+          <t>$682,595</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>May 31</t>
+          <t>Aug 25</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Diamond Films</t>
+          <t>Vértice 360</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6535,7 +6523,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Glimmers</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6555,27 +6543,27 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>$585,697</t>
+          <t>$604,555</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>$606,514</t>
+          <t>$616,979</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Oct 4</t>
+          <t>Apr 21</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Caramel Films</t>
+          <t>Bosco Films</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6592,7 +6580,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Lord of the Rings: The War of the Rohirrim</t>
+          <t>Love &amp; Revolution</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6612,27 +6600,27 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>$585,139</t>
+          <t>$596,486</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>$661,829</t>
+          <t>$597,467</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Dec 6</t>
+          <t>Jul 7</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Filmax</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6649,7 +6637,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The Blue Star</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6669,22 +6657,22 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>$571,172</t>
+          <t>$584,863</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>$593,495</t>
+          <t>$616,171</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Feb 23</t>
+          <t>Jan 6</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6706,7 +6694,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ellipsis</t>
+          <t>Chinas</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6726,27 +6714,27 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>$567,356</t>
+          <t>$516,819</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>$568,658</t>
+          <t>$537,187</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Sep 20</t>
+          <t>Oct 6</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6763,7 +6751,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Epic Tails</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6783,27 +6771,27 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>$563,959</t>
+          <t>$505,979</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>$564,274</t>
+          <t>$505,979</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Feb 23</t>
+          <t>May 12</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Selecta Visión</t>
+          <t>Notorious Pictures</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6820,7 +6808,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>La casa</t>
+          <t>Demon Slayer: Kimetsu No Yaiba - To the Swordsmith Village</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6840,27 +6828,27 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>$563,335</t>
+          <t>$499,220</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>$638,126</t>
+          <t>$605,569</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>May 3</t>
+          <t>Mar 3</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6877,7 +6865,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The Exorcism</t>
+          <t>Close Your Eyes</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6897,27 +6885,27 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>$549,290</t>
+          <t>$492,469</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>$549,290</t>
+          <t>$506,366</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>May 31</t>
+          <t>Sep 29</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>Avalon</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6934,7 +6922,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>The Crow</t>
+          <t>Mavka: The Forest Song</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6954,27 +6942,27 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>$527,587</t>
+          <t>$489,590</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>$527,587</t>
+          <t>$898,072</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Aug 30</t>
+          <t>Apr 28</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>TriPictures</t>
+          <t>Selecta Visión</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6991,7 +6979,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>The Hunger Games: The Ballad of Songbirds &amp; Snakes</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7011,27 +6999,27 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>$522,287</t>
+          <t>$468,694</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>$8,556,754</t>
+          <t>$468,694</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Nov 17</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7048,7 +7036,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>All of Us Strangers</t>
+          <t>Master Gardener</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7068,27 +7056,27 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>$516,851</t>
+          <t>$440,334</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>$516,851</t>
+          <t>$440,334</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Feb 23</t>
+          <t>Jun 9</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Caramel Films</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7105,7 +7093,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hispanoamerica</t>
+          <t>A Brighter Tomorrow</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7125,27 +7113,27 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>$515,139</t>
+          <t>$438,119</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>$516,441</t>
+          <t>$439,356</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Apr 12</t>
+          <t>Sep 15</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Bosco Films</t>
+          <t>Caramel Films</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7162,7 +7150,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Topuria Matador</t>
+          <t>Strays</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7182,27 +7170,27 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>$509,422</t>
+          <t>$431,639</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>$546,718</t>
+          <t>$431,639</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Sep 20</t>
+          <t>Sep 22</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Filmax</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7219,7 +7207,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>May December</t>
+          <t>Esta ambición desmedida</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7239,27 +7227,27 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>$505,865</t>
+          <t>$427,447</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>$506,895</t>
+          <t>$482,142</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Feb 23</t>
+          <t>Oct 27</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Sun Distribution</t>
+          <t>Avalon</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7276,7 +7264,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mothers' Instinct</t>
+          <t>The Old Oak</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7296,27 +7284,27 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>$497,281</t>
+          <t>$415,398</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>$497,281</t>
+          <t>$417,975</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Jun 14</t>
+          <t>Nov 17</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>Vértigo Films</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7333,7 +7321,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Well Done!</t>
+          <t>The Black Demon</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7353,27 +7341,27 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>$479,108</t>
+          <t>$411,868</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>$483,198</t>
+          <t>$436,184</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Aug 23</t>
+          <t>Jul 7</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>DeAPlaneta</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7390,7 +7378,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>The Bikeriders</t>
+          <t>Verano en rojo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7410,27 +7398,27 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>$473,858</t>
+          <t>$411,184</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>$473,858</t>
+          <t>$411,227</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Jul 12</t>
+          <t>Sep 8</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>DeAPlaneta</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7447,7 +7435,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Decision to Leave</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7467,27 +7455,27 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>$464,782</t>
+          <t>$389,773</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>$548,323</t>
+          <t>$391,245</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Feb 16</t>
+          <t>Jan 20</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Avalon</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7504,7 +7492,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>The Teacher Who Promised the Sea</t>
+          <t>The Rye Horn</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7524,27 +7512,27 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>$458,515</t>
+          <t>$384,425</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>$1,818,956</t>
+          <t>$426,291</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Nov 10</t>
+          <t>Oct 13</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Filmax</t>
+          <t>Elastica</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7561,7 +7549,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>The Other Way Around</t>
+          <t>The Girls Are Alright</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7581,22 +7569,22 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>$443,405</t>
+          <t>$372,585</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>$443,742</t>
+          <t>$368,245</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Aug 30</t>
+          <t>Aug 25</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7618,7 +7606,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Megalopolis</t>
+          <t>Aftersun</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7638,27 +7626,27 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>$436,607</t>
+          <t>$366,910</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>$436,607</t>
+          <t>$503,032</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Sep 27</t>
+          <t>Dec 16</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>TriPictures</t>
+          <t>Elastica</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7675,7 +7663,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Afraid</t>
+          <t>The Eight Mountains</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7695,27 +7683,27 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>$430,456</t>
+          <t>$364,666</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>$430,456</t>
+          <t>$371,046</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Aug 30</t>
+          <t>May 19</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Avalon</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7732,7 +7720,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Here</t>
+          <t>The Quiet Girl</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7752,27 +7740,27 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>$426,624</t>
+          <t>$354,775</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>$450,446</t>
+          <t>$355,609</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Dec 5</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7789,7 +7777,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Oppenheimer</t>
+          <t>Marlowe</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7809,27 +7797,27 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>$406,831</t>
+          <t>$348,754</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>$23,066,528</t>
+          <t>$348,754</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Jul 21</t>
+          <t>May 12</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7846,7 +7834,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SuperKlaus</t>
+          <t>Retribution</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7866,27 +7854,27 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>$383,193</t>
+          <t>$345,764</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>$420,489</t>
+          <t>$345,764</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Dec 6</t>
+          <t>Oct 27</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Filmax</t>
+          <t>TriPictures</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7903,7 +7891,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nefarious</t>
+          <t>Kandahar</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7923,27 +7911,27 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>$381,812</t>
+          <t>$342,344</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>$381,828</t>
+          <t>$342,365</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Feb 2</t>
+          <t>Jun 16</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>European Dreams Factory</t>
+          <t>DeAPlaneta</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7960,7 +7948,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>La Joia: Bad Gyal</t>
+          <t>The Crime Is Mine</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7980,27 +7968,27 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>$376,735</t>
+          <t>$334,991</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>$469,962</t>
+          <t>$338,684</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>May 5</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Avalon</t>
+          <t>Caramel Films</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8017,7 +8005,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Monkey Man</t>
+          <t>Maybe I Do</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8037,27 +8025,27 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>$365,437</t>
+          <t>$333,770</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>$365,437</t>
+          <t>$333,849</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Apr 12</t>
+          <t>Apr 21</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Diamond Films</t>
+          <t>Beta Fiction Spain</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8074,7 +8062,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sin instrucciones</t>
+          <t>Beautiful Disaster</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8094,27 +8082,27 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>$364,944</t>
+          <t>$329,051</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>$1,420,507</t>
+          <t>$331,841</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Dec 27</t>
+          <t>Apr 14</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,7 +8119,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Butterfly Tale</t>
+          <t>The Offering</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8151,27 +8139,27 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>$356,179</t>
+          <t>$306,042</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>$356,276</t>
+          <t>$306,082</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Jan 26</t>
+          <t>Jan 27</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Flins &amp; Piniculas</t>
+          <t>Vértice 360</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8188,7 +8176,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>The Inseparables</t>
+          <t>Renfield</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8208,27 +8196,27 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>$352,812</t>
+          <t>$304,782</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>$353,574</t>
+          <t>$304,782</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Aug 30</t>
+          <t>Apr 14</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8245,7 +8233,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>La Chimera</t>
+          <t>Terrifier 2</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8265,27 +8253,27 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>$346,056</t>
+          <t>$304,628</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>$348,819</t>
+          <t>$304,731</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Apr 19</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Elastica</t>
+          <t>Selecta Visión</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8302,7 +8290,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Birds Flying East</t>
+          <t>Los buenos modales</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8322,27 +8310,27 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>$337,425</t>
+          <t>$298,975</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>$526,007</t>
+          <t>$298,975</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Apr 5</t>
+          <t>Apr 28</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Filmax</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8359,7 +8347,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>The Promised Land</t>
+          <t>Poker Face</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8379,27 +8367,27 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>$337,196</t>
+          <t>$295,812</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>$338,585</t>
+          <t>$295,868</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Feb 2</t>
+          <t>Jan 13</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Vértice 360</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8416,7 +8404,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Samana Sunrise</t>
+          <t>The Movie Teller</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8436,27 +8424,27 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>$336,343</t>
+          <t>$291,670</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>$336,343</t>
+          <t>$295,660</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Nov 8</t>
+          <t>Oct 27</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8473,7 +8461,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Saturn Return</t>
+          <t>Inspector Sun</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8493,27 +8481,27 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>$333,736</t>
+          <t>$285,612</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>$349,698</t>
+          <t>$409,672</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>May 24</t>
+          <t>Dec 30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>TriPictures</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8530,7 +8518,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Hit Man</t>
+          <t>Book Club: The Next Chapter</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8550,27 +8538,27 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>$330,527</t>
+          <t>$275,752</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>$402,498</t>
+          <t>$275,752</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Jun 7</t>
+          <t>May 12</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Diamond Films</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8587,7 +8575,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Next Goal Wins</t>
+          <t>Empire of Light</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8607,27 +8595,27 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>$329,270</t>
+          <t>$272,022</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>$667,510</t>
+          <t>$272,022</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Dec 29</t>
+          <t>Mar 31</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Walt Disney Studios Motion Pictures</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8644,7 +8632,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Cocorico</t>
+          <t>Dumb Money</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8664,27 +8652,27 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>$327,326</t>
+          <t>$262,766</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>$422,568</t>
+          <t>$262,866</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>May 3</t>
+          <t>Oct 5</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>TriPictures</t>
+          <t>DeAPlaneta</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8701,7 +8689,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Horizon: An American Saga - Chapter 1</t>
+          <t>Bed Rest</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8721,27 +8709,27 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>$322,167</t>
+          <t>$259,104</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>$322,167</t>
+          <t>$279,523</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Jun 28</t>
+          <t>Jul 7</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8758,7 +8746,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>The Three Musketeers - Part II: Milady</t>
+          <t>Jump!</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8778,27 +8766,27 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>$322,083</t>
+          <t>$253,346</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>$322,363</t>
+          <t>$253,446</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Jan 26</t>
+          <t>Sep 1</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8815,7 +8803,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Free Falling</t>
+          <t>Matria</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8835,27 +8823,27 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>$312,682</t>
+          <t>$246,038</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>$312,682</t>
+          <t>$245,319</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>May 17</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Avalon</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8872,7 +8860,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Howl's Moving Castle2024 Re-release</t>
+          <t>Strange Way of Life</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8892,27 +8880,27 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>$305,644</t>
+          <t>$243,897</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>181</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>$354,214</t>
+          <t>$244,525</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Jul 12</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Vértigo Films</t>
+          <t>BTeam Pictures</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8929,7 +8917,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Por tus muertos</t>
+          <t>Lobo feroz</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8949,27 +8937,27 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>$294,398</t>
+          <t>$236,751</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>$294,398</t>
+          <t>$237,053</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Mar 8</t>
+          <t>Jan 27</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Walt Disney Pictures</t>
+          <t>Filmax</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -8986,7 +8974,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Elli and Her Monster Team</t>
+          <t>Heaven Can't Wait</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9006,27 +8994,27 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>$287,024</t>
+          <t>$236,002</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>$295,542</t>
+          <t>$278,252</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Nov 1</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Flins &amp; Piniculas</t>
+          <t>European Dreams Factory</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9043,7 +9031,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>White Bird</t>
+          <t>Under Therapy</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9063,27 +9051,27 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>$276,144</t>
+          <t>$230,777</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>$276,144</t>
+          <t>$239,457</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Oct 4</t>
+          <t>Mar 17</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Diamond Films</t>
+          <t>Syldavia Cinema</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9100,7 +9088,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Haunted Heart</t>
+          <t>Creatura</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9120,27 +9108,27 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>$275,951</t>
+          <t>$221,118</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>$277,503</t>
+          <t>$239,746</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Aug 23</t>
+          <t>Sep 8</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Avalon</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9157,7 +9145,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>When Fall Is Coming</t>
+          <t>The Lord of the Rings: The Return of the King2023 Re-release (20th Anniversary)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9177,27 +9165,27 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>$273,856</t>
+          <t>$218,089</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>$322,577</t>
+          <t>$218,089</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Dec 13</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9214,7 +9202,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Robot Dreams</t>
+          <t>Devotion</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9234,27 +9222,27 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>$266,330</t>
+          <t>$216,326</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>$504,100</t>
+          <t>$216,326</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Dec 8</t>
+          <t>Jan 27</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Diamond Films</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9271,7 +9259,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>¿Es el enemigo? La película de Gila</t>
+          <t>Una vida no tan simple</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9291,27 +9279,27 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>$265,021</t>
+          <t>$215,171</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>$306,302</t>
+          <t>$224,158</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Dec 13</t>
+          <t>Jun 23</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Filmax</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9328,7 +9316,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Shin Jigen! Crayon Shin-chan the Movie</t>
+          <t>The Lord of the Rings: The Two Towers2023 Re-release</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9348,27 +9336,27 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>$263,848</t>
+          <t>$211,284</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>$264,755</t>
+          <t>$243,868</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Oct 18</t>
+          <t>Nov 17</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Alfa Films</t>
+          <t>Warner Bros.</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9385,7 +9373,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Disco, Ibiza, Locomia</t>
+          <t>Watcher</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9405,27 +9393,27 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>$258,896</t>
+          <t>$210,901</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>$259,817</t>
+          <t>$210,901</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>May 17</t>
+          <t>Mar 17</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9442,7 +9430,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Harold and the Purple Crayon</t>
+          <t>Just Super</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9462,27 +9450,27 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>$253,374</t>
+          <t>$210,261</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>$253,374</t>
+          <t>$210,261</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Nov 8</t>
+          <t>Jun 16</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>VerCine</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9499,7 +9487,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Noah's Ark</t>
+          <t>Love Again</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9519,27 +9507,27 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>$252,448</t>
+          <t>$206,710</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>$252,448</t>
+          <t>$206,710</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Jan 19</t>
+          <t>May 12</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Beta Fiction Spain</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9556,7 +9544,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Puan</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9576,27 +9564,27 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>$252,443</t>
+          <t>$200,202</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>$299,469</t>
+          <t>$203,197</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Mar 29</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BTeam Pictures</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9613,7 +9601,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>The Taste of Things</t>
+          <t>The Tenderness</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9633,27 +9621,27 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>$251,736</t>
+          <t>$198,071</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>$434,442</t>
+          <t>$198,071</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Dec 22</t>
+          <t>Sep 29</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9670,7 +9658,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Interstellar</t>
+          <t>Jeepers Creepers: Reborn</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9690,27 +9678,27 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>$247,743</t>
+          <t>$197,029</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>$11,196,348</t>
+          <t>$197,029</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Nov 7</t>
+          <t>May 12</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Warner Bros.</t>
+          <t>Selecta Visión</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9727,7 +9715,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Freud's Last Session</t>
+          <t>My Fairy Troublemaker</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9747,27 +9735,27 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>$246,728</t>
+          <t>$191,976</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>$251,348</t>
+          <t>$191,976</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Jun 7</t>
+          <t>Mar 10</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Selecta Visión</t>
+          <t>Beta Fiction Spain</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9784,7 +9772,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sleeping Dogs</t>
+          <t>Tad the Lost Explorer and the Emerald Tablet</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9804,27 +9792,27 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>$246,550</t>
+          <t>$190,217</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>$246,603</t>
+          <t>$12,825,834</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Jun 14</t>
+          <t>Aug 26</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Youplanet Pictures</t>
+          <t>Paramount Pictures International</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9841,7 +9829,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ennio Doris - C'è anche domani</t>
+          <t>Robot Dreams</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9861,22 +9849,22 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>$243,480</t>
+          <t>$190,020</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>$1,193,380</t>
+          <t>$567,300</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>Dec 8</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9898,7 +9886,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>In the Land of Saints and Sinners</t>
+          <t>Knights of the Zodiac</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9918,27 +9906,27 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>$242,898</t>
+          <t>$188,036</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>$278,594</t>
+          <t>$188,036</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Jul 5</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -9955,7 +9943,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Spy x Family Code: White</t>
+          <t>Holy Spider</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9975,27 +9963,27 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>$241,853</t>
+          <t>$186,684</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>$241,853</t>
+          <t>$186,880</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Apr 19</t>
+          <t>Jan 13</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Karma Films</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10012,7 +10000,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Wicked Little Letters</t>
+          <t>The Son</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10032,27 +10020,27 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>$238,670</t>
+          <t>$185,810</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>$440,054</t>
+          <t>$185,810</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Apr 5</t>
+          <t>Mar 3</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Diamond Films</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10069,7 +10057,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>When Evil Lurks</t>
+          <t>Godland</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10089,27 +10077,27 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>$237,957</t>
+          <t>$185,712</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>$237,957</t>
+          <t>$188,228</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Jan 19</t>
+          <t>Aug 11</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Selecta Visión</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10126,7 +10114,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Love Lies Bleeding</t>
+          <t>Godzilla Minus One</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10146,27 +10134,27 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>$219,761</t>
+          <t>$182,427</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>$223,042</t>
+          <t>$227,853</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Apr 12</t>
+          <t>Dec 15</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Avalon</t>
+          <t>Piece of Magic Entertainment</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10183,7 +10171,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Out of Season</t>
+          <t>The Taste of Things</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10203,27 +10191,27 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>$216,136</t>
+          <t>$173,164</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>$223,370</t>
+          <t>$434,442</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Jul 5</t>
+          <t>Dec 22</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10240,7 +10228,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Last Stop: Rocafort St.</t>
+          <t>About My Father</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10260,27 +10248,27 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>$212,192</t>
+          <t>$172,209</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>$212,557</t>
+          <t>$172,209</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Sep 6</t>
+          <t>Jun 9</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Filmax</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10297,7 +10285,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Litle Loves</t>
+          <t>Women Talking</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10317,27 +10305,27 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>$211,683</t>
+          <t>$169,518</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>$200,148</t>
+          <t>$169,518</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Mar 8</t>
+          <t>Feb 17</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10354,7 +10342,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Raqa</t>
+          <t>Silent Night</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10374,22 +10362,22 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>$203,577</t>
+          <t>$167,533</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>179</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>$204,132</t>
+          <t>$167,715</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Nov 22</t>
+          <t>Dec 1</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10411,7 +10399,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>The Miracle Club</t>
+          <t>They Shot the Piano Player</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10431,27 +10419,27 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>$201,775</t>
+          <t>$167,080</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>$202,802</t>
+          <t>$170,598</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Oct 18</t>
+          <t>Oct 6</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>BTeam Pictures</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10468,7 +10456,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>El Llanto</t>
+          <t>Speak Sunlight</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10488,27 +10476,27 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>$193,481</t>
+          <t>$160,254</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>$208,999</t>
+          <t>$160,254</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Sep 22</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Universal Pictures International (UPI)</t>
+          <t>Adso Films</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10525,7 +10513,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>The Boogeyman: The Origin of the Myth</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10545,27 +10533,27 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>$192,435</t>
+          <t>$157,844</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>$212,768</t>
+          <t>$157,964</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Jun 21</t>
+          <t>Aug 11</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>Filmax</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10582,7 +10570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>A Real Job</t>
+          <t>Golda</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10602,27 +10590,27 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>$181,411</t>
+          <t>$157,126</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>$183,263</t>
+          <t>$157,126</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>May 17</t>
+          <t>Dec 15</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Filmax</t>
+          <t>Sun Distribution</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10639,7 +10627,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Io Capitano</t>
+          <t>Jeanne du Barry</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10659,27 +10647,27 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>$175,745</t>
+          <t>$150,955</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>$207,541</t>
+          <t>$150,955</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Jan 5</t>
+          <t>Sep 22</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Caramel Films</t>
+          <t>Notorious Pictures</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10696,7 +10684,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>The Bricklayer</t>
+          <t>Next Goal Wins</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10716,27 +10704,27 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>$173,550</t>
+          <t>$149,340</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>$228,566</t>
+          <t>$667,510</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Jan 5</t>
+          <t>Dec 29</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>Walt Disney Pictures</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10753,7 +10741,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Run, Tiger Run!</t>
+          <t>Monster</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10773,27 +10761,27 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>$172,356</t>
+          <t>$147,042</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>$172,356</t>
+          <t>$147,785</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Feb 9</t>
+          <t>Sep 29</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vértigo Films</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -10810,7 +10798,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Irena's Vow</t>
+          <t>Whitney Houston: I Wanna Dance with Somebody</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10830,27 +10818,27 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>$162,167</t>
+          <t>$144,982</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>$162,258</t>
+          <t>$512,023</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>May 31</t>
+          <t>Dec 23</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -10867,7 +10855,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ex-Husbands</t>
+          <t>Cairo Conspiracy</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10887,27 +10875,27 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>$160,480</t>
+          <t>$141,870</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>$161,280</t>
+          <t>$141,870</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Jun 7</t>
+          <t>Apr 14</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Avalon</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -10924,7 +10912,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Goebbels and the Führer</t>
+          <t>Siege</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10944,27 +10932,27 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>$158,269</t>
+          <t>$141,748</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>$159,521</t>
+          <t>$141,748</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Nov 29</t>
+          <t>May 5</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -10981,7 +10969,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Autumn and the Black Jaguar</t>
+          <t>The Enchanted</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11001,27 +10989,27 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>$156,855</t>
+          <t>$132,729</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>$156,855</t>
+          <t>$132,061</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Apr 12</t>
+          <t>Jun 2</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>TriPictures</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11038,7 +11026,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Mala persona</t>
+          <t>She Said</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11058,27 +11046,27 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>$155,056</t>
+          <t>$128,869</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>$179,265</t>
+          <t>$210,891</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Jul 5</t>
+          <t>Dec 30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Filmax</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11095,7 +11083,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Never Let Go</t>
+          <t>Till</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11115,27 +11103,27 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>$153,584</t>
+          <t>$125,881</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>$153,584</t>
+          <t>$125,881</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Nov 15</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Vértice 360</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11152,7 +11140,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Et la fête continue!</t>
+          <t>Champions</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11172,27 +11160,27 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>$152,273</t>
+          <t>$123,750</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>$161,148</t>
+          <t>$125,686</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Dec 15</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Universal Pictures International (UPI)</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11209,7 +11197,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>The Great Escaper</t>
+          <t>Upon Entry</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11229,27 +11217,27 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>$150,483</t>
+          <t>$122,201</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>$150,483</t>
+          <t>$122,759</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Jun 16</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Diamond Films</t>
+          <t>Karma Films</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11266,7 +11254,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Parthenope</t>
+          <t>Something Is About to Happen</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11286,27 +11274,27 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>$146,927</t>
+          <t>$120,651</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>$742,037</t>
+          <t>$125,125</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Dec 27</t>
+          <t>Nov 17</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>BTeam Pictures</t>
+          <t>Wanda Visión S.A.</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11323,7 +11311,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>One Direction: This Is Us</t>
+          <t>Let the Dance Begin</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11343,27 +11331,27 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>$144,678</t>
+          <t>$119,809</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>$1,043,295</t>
+          <t>$126,154</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Aug 30</t>
+          <t>Apr 7</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Me Lo Creo Distribución</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11380,7 +11368,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Dream Scenario</t>
+          <t>Doraemon the Movie: Nobita's New Dinosaur</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11400,27 +11388,27 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>$142,436</t>
+          <t>$118,958</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>$142,572</t>
+          <t>$276,184</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Mar 1</t>
+          <t>Nov 10</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Vértigo Films</t>
+          <t>Alfa Films</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11437,7 +11425,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Verano en diciembre</t>
+          <t>Journey to Bethlehem</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11457,27 +11445,27 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>$139,902</t>
+          <t>$118,548</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>$144,469</t>
+          <t>$118,548</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Nov 8</t>
+          <t>Dec 15</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Vertigo Films</t>
+          <t>Sony Pictures Releasing</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11494,7 +11482,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Coraline15th Anniversary</t>
+          <t>Rally Road Racers</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11514,27 +11502,27 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>$139,769</t>
+          <t>$116,952</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>$216,422</t>
+          <t>$117,058</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Jul 28</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Versión Digital</t>
+          <t>Vértigo Films</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11551,7 +11539,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>My Hero Academia: You're Next</t>
+          <t>Driving Madeleine</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11571,27 +11559,27 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>$136,984</t>
+          <t>$116,876</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>$136,984</t>
+          <t>$117,242</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Oct 11</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>A Contracorriente Films</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -11608,7 +11596,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Yo no soy esa</t>
+          <t>Tin &amp; Tina</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11628,27 +11616,27 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>$135,159</t>
+          <t>$112,392</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>$142,628</t>
+          <t>$112,450</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Nov 1</t>
+          <t>Mar 31</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Sony Pictures Releasing</t>
+          <t>Filmax</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11665,7 +11653,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>The Flamenco Guitar of Yerai Cortés</t>
+          <t>The Portable Door</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11685,27 +11673,27 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>$131,849</t>
+          <t>$111,284</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>$474,407</t>
+          <t>$111,293</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Dec 20</t>
+          <t>Jun 23</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>A Contracorriente Films</t>
+          <t>DeAPlaneta</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11722,7 +11710,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Hotel Bitcoin</t>
+          <t>Un cel de plom</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11742,27 +11730,27 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>$131,186</t>
+          <t>$110,656</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>$131,186</t>
+          <t>$110,656</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Sep 13</t>
+          <t>Apr 28</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>DeAPlaneta</t>
+          <t>Filmax</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -11779,7 +11767,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>The Quiet Maid</t>
+          <t>Fallen Leaves</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11799,27 +11787,27 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>$127,183</t>
+          <t>$109,607</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>$129,152</t>
+          <t>$781,961</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>May 17</t>
+          <t>Dec 29</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Karma Films</t>
+          <t>Avalon</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -11836,7 +11824,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Haunting of the Queen Mary</t>
+          <t>In the Company of Women</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11856,27 +11844,27 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>$126,043</t>
+          <t>$107,681</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>56</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>$126,043</t>
+          <t>$108,979</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Dec 13</t>
+          <t>May 5</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Diamond Films</t>
+          <t>Filmax</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
